--- a/outputs/59196.xlsx
+++ b/outputs/59196.xlsx
@@ -116,12 +116,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -318,73 +322,73 @@
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX(D3:G3),D3:G3,0))</f>
+      <c r="H3" s="2" t="str">
+        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D3:G3), D3:G3, 0))</f>
         <v>D</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX(D4:G4),D4:G4,0))</f>
+      <c r="H4" s="2" t="str">
+        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D4:G4), D4:G4, 0))</f>
         <v>A</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX(D5:G5),D5:G5,0))</f>
+      <c r="H5" s="2" t="str">
+        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D5:G5), D5:G5, 0))</f>
         <v>D</v>
       </c>
     </row>

--- a/outputs/59196.xlsx
+++ b/outputs/59196.xlsx
@@ -125,7 +125,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,7 +321,7 @@
   <dimension ref="D2:H5"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
@@ -338,7 +338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
@@ -352,11 +352,11 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="str">
-        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D3:G3), D3:G3, 0))</f>
+        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX($D3:$G3),$D3:$G3,0))</f>
         <v>D</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D4" s="1" t="n">
         <v>2</v>
       </c>
@@ -370,11 +370,11 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D4:G4), D4:G4, 0))</f>
+        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX($D4:$G4),$D4:$G4,0))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
@@ -388,7 +388,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="str">
-        <f aca="false">INDEX($D$2:$G$2, MATCH(MAX(D5:G5), D5:G5, 0))</f>
+        <f aca="false">INDEX($D$2:$G$2,MATCH(MAX($D5:$G5),$D5:$G5,0))</f>
         <v>D</v>
       </c>
     </row>
